--- a/research/traditional_assets/database/data/kenya/kenya_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_investments_asset_management.xlsx
@@ -615,7 +615,7 @@
         <v>6.9</v>
       </c>
       <c r="N2">
-        <v>0.08323281061519903</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="O2">
         <v>1.088328075709779</v>
@@ -624,7 +624,7 @@
         <v>6.9</v>
       </c>
       <c r="Q2">
-        <v>0.08323281061519903</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="R2">
         <v>1.088328075709779</v>
@@ -639,16 +639,16 @@
         <v>39.7</v>
       </c>
       <c r="V2">
-        <v>0.4788902291917974</v>
+        <v>0.8802660753880266</v>
       </c>
       <c r="W2">
         <v>0.01377661886136462</v>
       </c>
       <c r="X2">
-        <v>0.2195728428108816</v>
+        <v>0.450494239600425</v>
       </c>
       <c r="Y2">
-        <v>-0.2057962239495169</v>
+        <v>-0.4367176207390604</v>
       </c>
       <c r="Z2">
         <v>0.1408205290670046</v>
@@ -657,10 +657,10 @@
         <v>0.01916679866941232</v>
       </c>
       <c r="AB2">
-        <v>0.09313991545828257</v>
+        <v>0.1459558016330965</v>
       </c>
       <c r="AC2">
-        <v>-0.07397311678887025</v>
+        <v>-0.1267890029636842</v>
       </c>
       <c r="AD2">
         <v>238.1</v>
@@ -675,13 +675,13 @@
         <v>198.4</v>
       </c>
       <c r="AH2">
-        <v>0.7417445482866043</v>
+        <v>0.8407485875706214</v>
       </c>
       <c r="AI2">
         <v>0.3619641228336881</v>
       </c>
       <c r="AJ2">
-        <v>0.7052968361180235</v>
+        <v>0.8147843942505133</v>
       </c>
       <c r="AK2">
         <v>0.3209836596020061</v>
@@ -749,7 +749,7 @@
         <v>6.9</v>
       </c>
       <c r="N3">
-        <v>0.08323281061519903</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="O3">
         <v>1.088328075709779</v>
@@ -758,7 +758,7 @@
         <v>6.9</v>
       </c>
       <c r="Q3">
-        <v>0.08323281061519903</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="R3">
         <v>1.088328075709779</v>
@@ -773,16 +773,16 @@
         <v>39.7</v>
       </c>
       <c r="V3">
-        <v>0.4788902291917974</v>
+        <v>0.8802660753880266</v>
       </c>
       <c r="W3">
         <v>0.01377661886136462</v>
       </c>
       <c r="X3">
-        <v>0.2195728428108816</v>
+        <v>0.450494239600425</v>
       </c>
       <c r="Y3">
-        <v>-0.2057962239495169</v>
+        <v>-0.4367176207390604</v>
       </c>
       <c r="Z3">
         <v>0.1408205290670046</v>
@@ -791,10 +791,10 @@
         <v>0.01916679866941232</v>
       </c>
       <c r="AB3">
-        <v>0.09313991545828257</v>
+        <v>0.1459558016330965</v>
       </c>
       <c r="AC3">
-        <v>-0.07397311678887025</v>
+        <v>-0.1267890029636842</v>
       </c>
       <c r="AD3">
         <v>238.1</v>
@@ -809,13 +809,13 @@
         <v>198.4</v>
       </c>
       <c r="AH3">
-        <v>0.7417445482866043</v>
+        <v>0.8407485875706214</v>
       </c>
       <c r="AI3">
         <v>0.3619641228336881</v>
       </c>
       <c r="AJ3">
-        <v>0.7052968361180235</v>
+        <v>0.8147843942505133</v>
       </c>
       <c r="AK3">
         <v>0.3209836596020061</v>

--- a/research/traditional_assets/database/data/kenya/kenya_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_investments_asset_management.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.165</v>
-      </c>
-      <c r="E2">
-        <v>-0.383</v>
+        <v>-0.107</v>
       </c>
       <c r="G2">
-        <v>-0.02924634420697413</v>
+        <v>-0.09645569620253165</v>
       </c>
       <c r="H2">
-        <v>-0.02924634420697413</v>
+        <v>-0.09645569620253165</v>
       </c>
       <c r="I2">
-        <v>0.1361079865016873</v>
+        <v>-0.1392405063291139</v>
       </c>
       <c r="J2">
-        <v>0.1361079865016873</v>
+        <v>-0.1392405063291139</v>
       </c>
       <c r="K2">
-        <v>6.34</v>
+        <v>-22.4</v>
       </c>
       <c r="L2">
-        <v>0.07131608548931383</v>
+        <v>-0.2835443037974683</v>
       </c>
       <c r="M2">
-        <v>6.9</v>
+        <v>2.888</v>
       </c>
       <c r="N2">
-        <v>0.1529933481152993</v>
+        <v>0.0815819209039548</v>
       </c>
       <c r="O2">
-        <v>1.088328075709779</v>
+        <v>-0.1289285714285714</v>
       </c>
       <c r="P2">
-        <v>6.9</v>
+        <v>2.64</v>
       </c>
       <c r="Q2">
-        <v>0.1529933481152993</v>
+        <v>0.07457627118644068</v>
       </c>
       <c r="R2">
-        <v>1.088328075709779</v>
+        <v>-0.1178571428571429</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.2479999999999998</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.08587257617728525</v>
       </c>
       <c r="U2">
-        <v>39.7</v>
+        <v>14.3</v>
       </c>
       <c r="V2">
-        <v>0.8802660753880266</v>
+        <v>0.4039548022598871</v>
       </c>
       <c r="W2">
-        <v>0.01377661886136462</v>
+        <v>-0.0603936370989485</v>
       </c>
       <c r="X2">
-        <v>0.450494239600425</v>
+        <v>0.2817988543858247</v>
       </c>
       <c r="Y2">
-        <v>-0.4367176207390604</v>
+        <v>-0.3421924914847733</v>
       </c>
       <c r="Z2">
-        <v>0.1408205290670046</v>
+        <v>0.1468510669938285</v>
       </c>
       <c r="AA2">
-        <v>0.01916679866941232</v>
+        <v>-0.02044761692319131</v>
       </c>
       <c r="AB2">
-        <v>0.1459558016330965</v>
+        <v>0.1314289974979354</v>
       </c>
       <c r="AC2">
-        <v>-0.1267890029636842</v>
+        <v>-0.1518766144211267</v>
       </c>
       <c r="AD2">
-        <v>238.1</v>
+        <v>119.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>238.1</v>
+        <v>119.9</v>
       </c>
       <c r="AG2">
-        <v>198.4</v>
+        <v>105.6</v>
       </c>
       <c r="AH2">
-        <v>0.8407485875706214</v>
+        <v>0.7720540888602704</v>
       </c>
       <c r="AI2">
-        <v>0.3619641228336881</v>
+        <v>0.316776750330251</v>
       </c>
       <c r="AJ2">
-        <v>0.8147843942505133</v>
+        <v>0.748936170212766</v>
       </c>
       <c r="AK2">
-        <v>0.3209836596020061</v>
+        <v>0.2899505766062603</v>
       </c>
       <c r="AL2">
-        <v>21.8</v>
+        <v>28.6</v>
       </c>
       <c r="AM2">
-        <v>21.8</v>
+        <v>24.77</v>
       </c>
       <c r="AN2">
-        <v>19.048</v>
+        <v>-13.08951965065502</v>
       </c>
       <c r="AO2">
-        <v>0.555045871559633</v>
+        <v>-0.3846153846153846</v>
       </c>
       <c r="AP2">
-        <v>15.872</v>
+        <v>-11.52838427947598</v>
       </c>
       <c r="AQ2">
-        <v>0.555045871559633</v>
+        <v>-0.4440855874041179</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centum Investment Company Limited (NASE:CTUM)</t>
+          <t>Centum Investment Company Plc (NASE:CTUM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.165</v>
-      </c>
-      <c r="E3">
-        <v>-0.383</v>
+        <v>-0.107</v>
       </c>
       <c r="G3">
-        <v>-0.02924634420697413</v>
+        <v>-0.09645569620253165</v>
       </c>
       <c r="H3">
-        <v>-0.02924634420697413</v>
+        <v>-0.09645569620253165</v>
       </c>
       <c r="I3">
-        <v>0.1361079865016873</v>
+        <v>-0.1392405063291139</v>
       </c>
       <c r="J3">
-        <v>0.1361079865016873</v>
+        <v>-0.1392405063291139</v>
       </c>
       <c r="K3">
-        <v>6.34</v>
+        <v>-22.4</v>
       </c>
       <c r="L3">
-        <v>0.07131608548931383</v>
+        <v>-0.2835443037974683</v>
       </c>
       <c r="M3">
-        <v>6.9</v>
+        <v>2.888</v>
       </c>
       <c r="N3">
-        <v>0.1529933481152993</v>
+        <v>0.0815819209039548</v>
       </c>
       <c r="O3">
-        <v>1.088328075709779</v>
+        <v>-0.1289285714285714</v>
       </c>
       <c r="P3">
-        <v>6.9</v>
+        <v>2.64</v>
       </c>
       <c r="Q3">
-        <v>0.1529933481152993</v>
+        <v>0.07457627118644068</v>
       </c>
       <c r="R3">
-        <v>1.088328075709779</v>
+        <v>-0.1178571428571429</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2479999999999998</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.08587257617728525</v>
       </c>
       <c r="U3">
-        <v>39.7</v>
+        <v>14.3</v>
       </c>
       <c r="V3">
-        <v>0.8802660753880266</v>
+        <v>0.4039548022598871</v>
       </c>
       <c r="W3">
-        <v>0.01377661886136462</v>
+        <v>-0.0603936370989485</v>
       </c>
       <c r="X3">
-        <v>0.450494239600425</v>
+        <v>0.2817988543858247</v>
       </c>
       <c r="Y3">
-        <v>-0.4367176207390604</v>
+        <v>-0.3421924914847733</v>
       </c>
       <c r="Z3">
-        <v>0.1408205290670046</v>
+        <v>0.1468510669938285</v>
       </c>
       <c r="AA3">
-        <v>0.01916679866941232</v>
+        <v>-0.02044761692319131</v>
       </c>
       <c r="AB3">
-        <v>0.1459558016330965</v>
+        <v>0.1314289974979354</v>
       </c>
       <c r="AC3">
-        <v>-0.1267890029636842</v>
+        <v>-0.1518766144211267</v>
       </c>
       <c r="AD3">
-        <v>238.1</v>
+        <v>119.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>238.1</v>
+        <v>119.9</v>
       </c>
       <c r="AG3">
-        <v>198.4</v>
+        <v>105.6</v>
       </c>
       <c r="AH3">
-        <v>0.8407485875706214</v>
+        <v>0.7720540888602704</v>
       </c>
       <c r="AI3">
-        <v>0.3619641228336881</v>
+        <v>0.316776750330251</v>
       </c>
       <c r="AJ3">
-        <v>0.8147843942505133</v>
+        <v>0.748936170212766</v>
       </c>
       <c r="AK3">
-        <v>0.3209836596020061</v>
+        <v>0.2899505766062603</v>
       </c>
       <c r="AL3">
-        <v>21.8</v>
+        <v>28.6</v>
       </c>
       <c r="AM3">
-        <v>21.8</v>
+        <v>24.77</v>
       </c>
       <c r="AN3">
-        <v>19.048</v>
+        <v>-13.08951965065502</v>
       </c>
       <c r="AO3">
-        <v>0.555045871559633</v>
+        <v>-0.3846153846153846</v>
       </c>
       <c r="AP3">
-        <v>15.872</v>
+        <v>-11.52838427947598</v>
       </c>
       <c r="AQ3">
-        <v>0.555045871559633</v>
+        <v>-0.4440855874041179</v>
       </c>
     </row>
   </sheetData>
